--- a/format-laporan/hari-minggu-2026/Usulan Buka Rek PB Kab Maybrat 206 PB YOSUA KARETH.xlsx
+++ b/format-laporan/hari-minggu-2026/Usulan Buka Rek PB Kab Maybrat 206 PB YOSUA KARETH.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27928"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\Documents\BSPS\DATA KERJA PENDAMPING\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\BSPS-2026\format-laporan\hari-minggu-2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ACA580B1-83F2-481D-A252-1D7541282AC9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{830BBB74-F3C0-4350-AF68-097BAF23161A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="897" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="897" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet" sheetId="12" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1926" uniqueCount="794">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1918" uniqueCount="786">
   <si>
     <t>DAFTAR USULAN PEMBUKAAN REKENING PENERIMA BANTUAN BEDAH RUMAH</t>
   </si>
@@ -2387,30 +2387,6 @@
   </si>
   <si>
     <t>96050438</t>
-  </si>
-  <si>
-    <t>96050450</t>
-  </si>
-  <si>
-    <t>96050451</t>
-  </si>
-  <si>
-    <t>96050452</t>
-  </si>
-  <si>
-    <t>96050453</t>
-  </si>
-  <si>
-    <t>96050457</t>
-  </si>
-  <si>
-    <t>96050458</t>
-  </si>
-  <si>
-    <t>96050460</t>
-  </si>
-  <si>
-    <t>96050464</t>
   </si>
   <si>
     <t>STASTUS PERKAWINAN</t>
@@ -2601,12 +2577,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="14" fontId="5" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -2617,6 +2587,12 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="49" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2949,99 +2925,99 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A3:P214"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="6.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="15.7109375" style="2" customWidth="1"/>
-    <col min="3" max="3" width="34.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="6.54296875" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.7265625" style="2" customWidth="1"/>
+    <col min="3" max="3" width="34.453125" style="1" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="15" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="23.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="23.5703125" style="2" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="23.54296875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="23.54296875" style="2" bestFit="1" customWidth="1"/>
     <col min="7" max="8" width="19" style="1" customWidth="1"/>
     <col min="9" max="9" width="26" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="15.85546875" style="2" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="15.85546875" style="2" customWidth="1"/>
-    <col min="12" max="12" width="32.5703125" style="2" customWidth="1"/>
-    <col min="13" max="13" width="29.140625" style="2" customWidth="1"/>
-    <col min="14" max="14" width="27.140625" style="2" customWidth="1"/>
-    <col min="15" max="15" width="10.5703125" style="2" customWidth="1"/>
-    <col min="16" max="16" width="15.85546875" style="2" customWidth="1"/>
-    <col min="17" max="16384" width="8.85546875" style="2"/>
+    <col min="10" max="10" width="15.81640625" style="2" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="15.81640625" style="2" customWidth="1"/>
+    <col min="12" max="12" width="32.54296875" style="2" customWidth="1"/>
+    <col min="13" max="13" width="29.1796875" style="2" customWidth="1"/>
+    <col min="14" max="14" width="27.1796875" style="2" customWidth="1"/>
+    <col min="15" max="15" width="10.54296875" style="2" customWidth="1"/>
+    <col min="16" max="16" width="15.81640625" style="2" customWidth="1"/>
+    <col min="17" max="16384" width="8.81640625" style="2"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A3" s="28" t="s">
+    <row r="3" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A3" s="32" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="28"/>
-      <c r="C3" s="28"/>
-      <c r="D3" s="28"/>
-      <c r="E3" s="28"/>
-      <c r="F3" s="28"/>
-      <c r="G3" s="28"/>
-      <c r="H3" s="28"/>
-      <c r="I3" s="28"/>
-      <c r="J3" s="28"/>
-      <c r="K3" s="28"/>
-      <c r="L3" s="28"/>
-      <c r="M3" s="28"/>
-      <c r="N3" s="28"/>
-    </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A4" s="28" t="s">
+      <c r="B3" s="32"/>
+      <c r="C3" s="32"/>
+      <c r="D3" s="32"/>
+      <c r="E3" s="32"/>
+      <c r="F3" s="32"/>
+      <c r="G3" s="32"/>
+      <c r="H3" s="32"/>
+      <c r="I3" s="32"/>
+      <c r="J3" s="32"/>
+      <c r="K3" s="32"/>
+      <c r="L3" s="32"/>
+      <c r="M3" s="32"/>
+      <c r="N3" s="32"/>
+    </row>
+    <row r="4" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A4" s="32" t="s">
         <v>1</v>
       </c>
-      <c r="B4" s="28"/>
-      <c r="C4" s="28"/>
-      <c r="D4" s="28"/>
-      <c r="E4" s="28"/>
-      <c r="F4" s="28"/>
-      <c r="G4" s="28"/>
-      <c r="H4" s="28"/>
-      <c r="I4" s="28"/>
-      <c r="J4" s="28"/>
-      <c r="K4" s="28"/>
-      <c r="L4" s="28"/>
-      <c r="M4" s="28"/>
-      <c r="N4" s="28"/>
-    </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A5" s="29" t="s">
+      <c r="B4" s="32"/>
+      <c r="C4" s="32"/>
+      <c r="D4" s="32"/>
+      <c r="E4" s="32"/>
+      <c r="F4" s="32"/>
+      <c r="G4" s="32"/>
+      <c r="H4" s="32"/>
+      <c r="I4" s="32"/>
+      <c r="J4" s="32"/>
+      <c r="K4" s="32"/>
+      <c r="L4" s="32"/>
+      <c r="M4" s="32"/>
+      <c r="N4" s="32"/>
+    </row>
+    <row r="5" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A5" s="33" t="s">
         <v>21</v>
       </c>
-      <c r="B5" s="29"/>
-      <c r="C5" s="29"/>
-      <c r="D5" s="29"/>
-      <c r="E5" s="29"/>
-      <c r="F5" s="29"/>
-      <c r="G5" s="29"/>
-      <c r="H5" s="29"/>
-      <c r="I5" s="29"/>
-      <c r="J5" s="29"/>
-      <c r="K5" s="29"/>
-      <c r="L5" s="29"/>
-      <c r="M5" s="29"/>
-      <c r="N5" s="29"/>
-    </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A6" s="29" t="s">
+      <c r="B5" s="33"/>
+      <c r="C5" s="33"/>
+      <c r="D5" s="33"/>
+      <c r="E5" s="33"/>
+      <c r="F5" s="33"/>
+      <c r="G5" s="33"/>
+      <c r="H5" s="33"/>
+      <c r="I5" s="33"/>
+      <c r="J5" s="33"/>
+      <c r="K5" s="33"/>
+      <c r="L5" s="33"/>
+      <c r="M5" s="33"/>
+      <c r="N5" s="33"/>
+    </row>
+    <row r="6" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A6" s="33" t="s">
         <v>15</v>
       </c>
-      <c r="B6" s="29"/>
-      <c r="C6" s="29"/>
-      <c r="D6" s="29"/>
-      <c r="E6" s="29"/>
-      <c r="F6" s="29"/>
-      <c r="G6" s="29"/>
-      <c r="H6" s="29"/>
-      <c r="I6" s="29"/>
-      <c r="J6" s="29"/>
-      <c r="K6" s="29"/>
-      <c r="L6" s="29"/>
-      <c r="M6" s="29"/>
-      <c r="N6" s="29"/>
-    </row>
-    <row r="8" spans="1:16" ht="30" x14ac:dyDescent="0.25">
+      <c r="B6" s="33"/>
+      <c r="C6" s="33"/>
+      <c r="D6" s="33"/>
+      <c r="E6" s="33"/>
+      <c r="F6" s="33"/>
+      <c r="G6" s="33"/>
+      <c r="H6" s="33"/>
+      <c r="I6" s="33"/>
+      <c r="J6" s="33"/>
+      <c r="K6" s="33"/>
+      <c r="L6" s="33"/>
+      <c r="M6" s="33"/>
+      <c r="N6" s="33"/>
+    </row>
+    <row r="8" spans="1:16" ht="31" x14ac:dyDescent="0.35">
       <c r="A8" s="6" t="s">
         <v>2</v>
       </c>
@@ -3091,7 +3067,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A9" s="3">
         <v>1</v>
       </c>
@@ -3125,7 +3101,7 @@
       <c r="O9" s="5"/>
       <c r="P9" s="5"/>
     </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A10" s="3">
         <v>2</v>
       </c>
@@ -3159,7 +3135,7 @@
       <c r="O10" s="5"/>
       <c r="P10" s="5"/>
     </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A11" s="3">
         <v>3</v>
       </c>
@@ -3193,7 +3169,7 @@
       <c r="O11" s="5"/>
       <c r="P11" s="5"/>
     </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A12" s="3">
         <v>4</v>
       </c>
@@ -3227,7 +3203,7 @@
       <c r="O12" s="5"/>
       <c r="P12" s="5"/>
     </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A13" s="3">
         <v>5</v>
       </c>
@@ -3261,7 +3237,7 @@
       <c r="O13" s="5"/>
       <c r="P13" s="5"/>
     </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A14" s="3">
         <v>6</v>
       </c>
@@ -3295,7 +3271,7 @@
       <c r="O14" s="5"/>
       <c r="P14" s="5"/>
     </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A15" s="3">
         <v>7</v>
       </c>
@@ -3329,7 +3305,7 @@
       <c r="O15" s="5"/>
       <c r="P15" s="5"/>
     </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A16" s="3">
         <v>8</v>
       </c>
@@ -3363,7 +3339,7 @@
       <c r="O16" s="5"/>
       <c r="P16" s="5"/>
     </row>
-    <row r="17" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A17" s="3">
         <v>9</v>
       </c>
@@ -3397,7 +3373,7 @@
       <c r="O17" s="5"/>
       <c r="P17" s="5"/>
     </row>
-    <row r="18" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A18" s="3">
         <v>10</v>
       </c>
@@ -3431,7 +3407,7 @@
       <c r="O18" s="5"/>
       <c r="P18" s="5"/>
     </row>
-    <row r="19" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A19" s="3">
         <v>11</v>
       </c>
@@ -3465,7 +3441,7 @@
       <c r="O19" s="5"/>
       <c r="P19" s="5"/>
     </row>
-    <row r="20" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A20" s="3">
         <v>12</v>
       </c>
@@ -3499,7 +3475,7 @@
       <c r="O20" s="5"/>
       <c r="P20" s="5"/>
     </row>
-    <row r="21" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A21" s="3">
         <v>13</v>
       </c>
@@ -3533,7 +3509,7 @@
       <c r="O21" s="5"/>
       <c r="P21" s="5"/>
     </row>
-    <row r="22" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A22" s="3">
         <v>14</v>
       </c>
@@ -3567,7 +3543,7 @@
       <c r="O22" s="5"/>
       <c r="P22" s="5"/>
     </row>
-    <row r="23" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A23" s="3">
         <v>15</v>
       </c>
@@ -3601,7 +3577,7 @@
       <c r="O23" s="5"/>
       <c r="P23" s="5"/>
     </row>
-    <row r="24" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A24" s="3">
         <v>16</v>
       </c>
@@ -3635,7 +3611,7 @@
       <c r="O24" s="5"/>
       <c r="P24" s="5"/>
     </row>
-    <row r="25" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A25" s="3">
         <v>17</v>
       </c>
@@ -3669,7 +3645,7 @@
       <c r="O25" s="5"/>
       <c r="P25" s="5"/>
     </row>
-    <row r="26" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A26" s="3">
         <v>18</v>
       </c>
@@ -3703,7 +3679,7 @@
       <c r="O26" s="5"/>
       <c r="P26" s="5"/>
     </row>
-    <row r="27" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A27" s="3">
         <v>19</v>
       </c>
@@ -3737,7 +3713,7 @@
       <c r="O27" s="5"/>
       <c r="P27" s="5"/>
     </row>
-    <row r="28" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A28" s="3">
         <v>20</v>
       </c>
@@ -3771,7 +3747,7 @@
       <c r="O28" s="5"/>
       <c r="P28" s="5"/>
     </row>
-    <row r="29" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A29" s="3">
         <v>21</v>
       </c>
@@ -3805,7 +3781,7 @@
       <c r="O29" s="5"/>
       <c r="P29" s="5"/>
     </row>
-    <row r="30" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A30" s="3">
         <v>22</v>
       </c>
@@ -3839,7 +3815,7 @@
       <c r="O30" s="5"/>
       <c r="P30" s="5"/>
     </row>
-    <row r="31" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A31" s="3">
         <v>23</v>
       </c>
@@ -3873,7 +3849,7 @@
       <c r="O31" s="5"/>
       <c r="P31" s="5"/>
     </row>
-    <row r="32" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A32" s="3">
         <v>24</v>
       </c>
@@ -3907,7 +3883,7 @@
       <c r="O32" s="5"/>
       <c r="P32" s="5"/>
     </row>
-    <row r="33" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A33" s="3">
         <v>25</v>
       </c>
@@ -3941,7 +3917,7 @@
       <c r="O33" s="5"/>
       <c r="P33" s="5"/>
     </row>
-    <row r="34" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A34" s="3">
         <v>26</v>
       </c>
@@ -3975,7 +3951,7 @@
       <c r="O34" s="5"/>
       <c r="P34" s="5"/>
     </row>
-    <row r="35" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A35" s="3">
         <v>27</v>
       </c>
@@ -4009,7 +3985,7 @@
       <c r="O35" s="5"/>
       <c r="P35" s="5"/>
     </row>
-    <row r="36" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A36" s="3">
         <v>28</v>
       </c>
@@ -4043,7 +4019,7 @@
       <c r="O36" s="5"/>
       <c r="P36" s="5"/>
     </row>
-    <row r="37" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A37" s="3">
         <v>29</v>
       </c>
@@ -4077,7 +4053,7 @@
       <c r="O37" s="5"/>
       <c r="P37" s="5"/>
     </row>
-    <row r="38" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A38" s="3">
         <v>30</v>
       </c>
@@ -4111,7 +4087,7 @@
       <c r="O38" s="5"/>
       <c r="P38" s="5"/>
     </row>
-    <row r="39" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A39" s="3">
         <v>31</v>
       </c>
@@ -4145,7 +4121,7 @@
       <c r="O39" s="5"/>
       <c r="P39" s="5"/>
     </row>
-    <row r="40" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A40" s="3">
         <v>32</v>
       </c>
@@ -4179,7 +4155,7 @@
       <c r="O40" s="5"/>
       <c r="P40" s="5"/>
     </row>
-    <row r="41" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A41" s="3">
         <v>33</v>
       </c>
@@ -4213,7 +4189,7 @@
       <c r="O41" s="5"/>
       <c r="P41" s="5"/>
     </row>
-    <row r="42" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A42" s="3">
         <v>34</v>
       </c>
@@ -4247,7 +4223,7 @@
       <c r="O42" s="5"/>
       <c r="P42" s="5"/>
     </row>
-    <row r="43" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A43" s="3">
         <v>35</v>
       </c>
@@ -4281,7 +4257,7 @@
       <c r="O43" s="5"/>
       <c r="P43" s="5"/>
     </row>
-    <row r="44" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A44" s="3">
         <v>36</v>
       </c>
@@ -4315,7 +4291,7 @@
       <c r="O44" s="5"/>
       <c r="P44" s="5"/>
     </row>
-    <row r="45" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A45" s="3">
         <v>37</v>
       </c>
@@ -4349,7 +4325,7 @@
       <c r="O45" s="5"/>
       <c r="P45" s="5"/>
     </row>
-    <row r="46" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A46" s="3">
         <v>38</v>
       </c>
@@ -4383,7 +4359,7 @@
       <c r="O46" s="5"/>
       <c r="P46" s="5"/>
     </row>
-    <row r="47" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A47" s="3">
         <v>39</v>
       </c>
@@ -4417,7 +4393,7 @@
       <c r="O47" s="5"/>
       <c r="P47" s="5"/>
     </row>
-    <row r="48" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A48" s="3">
         <v>40</v>
       </c>
@@ -4451,7 +4427,7 @@
       <c r="O48" s="5"/>
       <c r="P48" s="5"/>
     </row>
-    <row r="49" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A49" s="3">
         <v>41</v>
       </c>
@@ -4485,7 +4461,7 @@
       <c r="O49" s="5"/>
       <c r="P49" s="5"/>
     </row>
-    <row r="50" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A50" s="3">
         <v>42</v>
       </c>
@@ -4519,7 +4495,7 @@
       <c r="O50" s="5"/>
       <c r="P50" s="5"/>
     </row>
-    <row r="51" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A51" s="3">
         <v>43</v>
       </c>
@@ -4553,7 +4529,7 @@
       <c r="O51" s="5"/>
       <c r="P51" s="5"/>
     </row>
-    <row r="52" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A52" s="3">
         <v>44</v>
       </c>
@@ -4587,7 +4563,7 @@
       <c r="O52" s="5"/>
       <c r="P52" s="5"/>
     </row>
-    <row r="53" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A53" s="3">
         <v>45</v>
       </c>
@@ -4621,7 +4597,7 @@
       <c r="O53" s="5"/>
       <c r="P53" s="5"/>
     </row>
-    <row r="54" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A54" s="3">
         <v>46</v>
       </c>
@@ -4655,7 +4631,7 @@
       <c r="O54" s="5"/>
       <c r="P54" s="5"/>
     </row>
-    <row r="55" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A55" s="3">
         <v>47</v>
       </c>
@@ -4689,7 +4665,7 @@
       <c r="O55" s="5"/>
       <c r="P55" s="5"/>
     </row>
-    <row r="56" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A56" s="3">
         <v>48</v>
       </c>
@@ -4723,7 +4699,7 @@
       <c r="O56" s="5"/>
       <c r="P56" s="5"/>
     </row>
-    <row r="57" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A57" s="3">
         <v>49</v>
       </c>
@@ -4757,7 +4733,7 @@
       <c r="O57" s="5"/>
       <c r="P57" s="5"/>
     </row>
-    <row r="58" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A58" s="3">
         <v>50</v>
       </c>
@@ -4791,7 +4767,7 @@
       <c r="O58" s="5"/>
       <c r="P58" s="5"/>
     </row>
-    <row r="59" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A59" s="3">
         <v>51</v>
       </c>
@@ -4825,7 +4801,7 @@
       <c r="O59" s="5"/>
       <c r="P59" s="5"/>
     </row>
-    <row r="60" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A60" s="3">
         <v>52</v>
       </c>
@@ -4859,7 +4835,7 @@
       <c r="O60" s="5"/>
       <c r="P60" s="5"/>
     </row>
-    <row r="61" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A61" s="3">
         <v>53</v>
       </c>
@@ -4893,7 +4869,7 @@
       <c r="O61" s="5"/>
       <c r="P61" s="5"/>
     </row>
-    <row r="62" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A62" s="3">
         <v>54</v>
       </c>
@@ -4927,7 +4903,7 @@
       <c r="O62" s="5"/>
       <c r="P62" s="5"/>
     </row>
-    <row r="63" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A63" s="3">
         <v>55</v>
       </c>
@@ -4961,7 +4937,7 @@
       <c r="O63" s="5"/>
       <c r="P63" s="5"/>
     </row>
-    <row r="64" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A64" s="3">
         <v>56</v>
       </c>
@@ -4995,7 +4971,7 @@
       <c r="O64" s="5"/>
       <c r="P64" s="5"/>
     </row>
-    <row r="65" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A65" s="3">
         <v>57</v>
       </c>
@@ -5029,7 +5005,7 @@
       <c r="O65" s="5"/>
       <c r="P65" s="5"/>
     </row>
-    <row r="66" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A66" s="3">
         <v>58</v>
       </c>
@@ -5063,7 +5039,7 @@
       <c r="O66" s="5"/>
       <c r="P66" s="5"/>
     </row>
-    <row r="67" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A67" s="3">
         <v>59</v>
       </c>
@@ -5097,7 +5073,7 @@
       <c r="O67" s="5"/>
       <c r="P67" s="5"/>
     </row>
-    <row r="68" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A68" s="3">
         <v>60</v>
       </c>
@@ -5131,7 +5107,7 @@
       <c r="O68" s="5"/>
       <c r="P68" s="5"/>
     </row>
-    <row r="69" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A69" s="3">
         <v>61</v>
       </c>
@@ -5165,7 +5141,7 @@
       <c r="O69" s="5"/>
       <c r="P69" s="5"/>
     </row>
-    <row r="70" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A70" s="3">
         <v>62</v>
       </c>
@@ -5199,7 +5175,7 @@
       <c r="O70" s="5"/>
       <c r="P70" s="5"/>
     </row>
-    <row r="71" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A71" s="3">
         <v>63</v>
       </c>
@@ -5233,7 +5209,7 @@
       <c r="O71" s="5"/>
       <c r="P71" s="5"/>
     </row>
-    <row r="72" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A72" s="3">
         <v>64</v>
       </c>
@@ -5267,7 +5243,7 @@
       <c r="O72" s="5"/>
       <c r="P72" s="5"/>
     </row>
-    <row r="73" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A73" s="3">
         <v>65</v>
       </c>
@@ -5301,7 +5277,7 @@
       <c r="O73" s="5"/>
       <c r="P73" s="5"/>
     </row>
-    <row r="74" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A74" s="3">
         <v>66</v>
       </c>
@@ -5335,7 +5311,7 @@
       <c r="O74" s="5"/>
       <c r="P74" s="5"/>
     </row>
-    <row r="75" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A75" s="3">
         <v>67</v>
       </c>
@@ -5369,7 +5345,7 @@
       <c r="O75" s="5"/>
       <c r="P75" s="5"/>
     </row>
-    <row r="76" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A76" s="3">
         <v>68</v>
       </c>
@@ -5403,7 +5379,7 @@
       <c r="O76" s="5"/>
       <c r="P76" s="5"/>
     </row>
-    <row r="77" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A77" s="3">
         <v>69</v>
       </c>
@@ -5437,7 +5413,7 @@
       <c r="O77" s="5"/>
       <c r="P77" s="5"/>
     </row>
-    <row r="78" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A78" s="3">
         <v>70</v>
       </c>
@@ -5471,7 +5447,7 @@
       <c r="O78" s="5"/>
       <c r="P78" s="5"/>
     </row>
-    <row r="79" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A79" s="3">
         <v>71</v>
       </c>
@@ -5505,7 +5481,7 @@
       <c r="O79" s="5"/>
       <c r="P79" s="5"/>
     </row>
-    <row r="80" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A80" s="3">
         <v>72</v>
       </c>
@@ -5539,7 +5515,7 @@
       <c r="O80" s="5"/>
       <c r="P80" s="5"/>
     </row>
-    <row r="81" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A81" s="3">
         <v>73</v>
       </c>
@@ -5573,7 +5549,7 @@
       <c r="O81" s="5"/>
       <c r="P81" s="5"/>
     </row>
-    <row r="82" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A82" s="3">
         <v>74</v>
       </c>
@@ -5607,7 +5583,7 @@
       <c r="O82" s="5"/>
       <c r="P82" s="5"/>
     </row>
-    <row r="83" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A83" s="3">
         <v>75</v>
       </c>
@@ -5641,7 +5617,7 @@
       <c r="O83" s="5"/>
       <c r="P83" s="5"/>
     </row>
-    <row r="84" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A84" s="3">
         <v>76</v>
       </c>
@@ -5675,7 +5651,7 @@
       <c r="O84" s="5"/>
       <c r="P84" s="5"/>
     </row>
-    <row r="85" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A85" s="3">
         <v>77</v>
       </c>
@@ -5709,7 +5685,7 @@
       <c r="O85" s="5"/>
       <c r="P85" s="5"/>
     </row>
-    <row r="86" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A86" s="3">
         <v>78</v>
       </c>
@@ -5743,7 +5719,7 @@
       <c r="O86" s="5"/>
       <c r="P86" s="5"/>
     </row>
-    <row r="87" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A87" s="12">
         <v>79</v>
       </c>
@@ -5777,7 +5753,7 @@
       <c r="O87" s="5"/>
       <c r="P87" s="5"/>
     </row>
-    <row r="88" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A88" s="3">
         <v>80</v>
       </c>
@@ -5811,7 +5787,7 @@
       <c r="O88" s="5"/>
       <c r="P88" s="5"/>
     </row>
-    <row r="89" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A89" s="3">
         <v>81</v>
       </c>
@@ -5845,7 +5821,7 @@
       <c r="O89" s="5"/>
       <c r="P89" s="5"/>
     </row>
-    <row r="90" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A90" s="3">
         <v>82</v>
       </c>
@@ -5879,7 +5855,7 @@
       <c r="O90" s="5"/>
       <c r="P90" s="5"/>
     </row>
-    <row r="91" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A91" s="3">
         <v>83</v>
       </c>
@@ -5913,7 +5889,7 @@
       <c r="O91" s="5"/>
       <c r="P91" s="5"/>
     </row>
-    <row r="92" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A92" s="3">
         <v>84</v>
       </c>
@@ -5947,7 +5923,7 @@
       <c r="O92" s="5"/>
       <c r="P92" s="5"/>
     </row>
-    <row r="93" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A93" s="3">
         <v>85</v>
       </c>
@@ -5981,7 +5957,7 @@
       <c r="O93" s="5"/>
       <c r="P93" s="5"/>
     </row>
-    <row r="94" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A94" s="3">
         <v>86</v>
       </c>
@@ -6015,7 +5991,7 @@
       <c r="O94" s="5"/>
       <c r="P94" s="5"/>
     </row>
-    <row r="95" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A95" s="3">
         <v>87</v>
       </c>
@@ -6049,7 +6025,7 @@
       <c r="O95" s="5"/>
       <c r="P95" s="5"/>
     </row>
-    <row r="96" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A96" s="3">
         <v>88</v>
       </c>
@@ -6083,7 +6059,7 @@
       <c r="O96" s="5"/>
       <c r="P96" s="5"/>
     </row>
-    <row r="97" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A97" s="3">
         <v>89</v>
       </c>
@@ -6117,7 +6093,7 @@
       <c r="O97" s="5"/>
       <c r="P97" s="5"/>
     </row>
-    <row r="98" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A98" s="3">
         <v>90</v>
       </c>
@@ -6151,7 +6127,7 @@
       <c r="O98" s="5"/>
       <c r="P98" s="5"/>
     </row>
-    <row r="99" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A99" s="3">
         <v>91</v>
       </c>
@@ -6185,7 +6161,7 @@
       <c r="O99" s="5"/>
       <c r="P99" s="5"/>
     </row>
-    <row r="100" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A100" s="3">
         <v>92</v>
       </c>
@@ -6219,7 +6195,7 @@
       <c r="O100" s="5"/>
       <c r="P100" s="5"/>
     </row>
-    <row r="101" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A101" s="3">
         <v>93</v>
       </c>
@@ -6253,7 +6229,7 @@
       <c r="O101" s="5"/>
       <c r="P101" s="5"/>
     </row>
-    <row r="102" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A102" s="3">
         <v>94</v>
       </c>
@@ -6287,7 +6263,7 @@
       <c r="O102" s="5"/>
       <c r="P102" s="5"/>
     </row>
-    <row r="103" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A103" s="3">
         <v>95</v>
       </c>
@@ -6321,7 +6297,7 @@
       <c r="O103" s="5"/>
       <c r="P103" s="5"/>
     </row>
-    <row r="104" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A104" s="3">
         <v>96</v>
       </c>
@@ -6355,7 +6331,7 @@
       <c r="O104" s="5"/>
       <c r="P104" s="5"/>
     </row>
-    <row r="105" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A105" s="3">
         <v>97</v>
       </c>
@@ -6389,7 +6365,7 @@
       <c r="O105" s="5"/>
       <c r="P105" s="5"/>
     </row>
-    <row r="106" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A106" s="3">
         <v>98</v>
       </c>
@@ -6423,7 +6399,7 @@
       <c r="O106" s="5"/>
       <c r="P106" s="5"/>
     </row>
-    <row r="107" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A107" s="3">
         <v>99</v>
       </c>
@@ -6457,7 +6433,7 @@
       <c r="O107" s="5"/>
       <c r="P107" s="5"/>
     </row>
-    <row r="108" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A108" s="3">
         <v>100</v>
       </c>
@@ -6491,7 +6467,7 @@
       <c r="O108" s="5"/>
       <c r="P108" s="5"/>
     </row>
-    <row r="109" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A109" s="3">
         <v>101</v>
       </c>
@@ -6525,7 +6501,7 @@
       <c r="O109" s="5"/>
       <c r="P109" s="5"/>
     </row>
-    <row r="110" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A110" s="3">
         <v>102</v>
       </c>
@@ -6559,7 +6535,7 @@
       <c r="O110" s="5"/>
       <c r="P110" s="5"/>
     </row>
-    <row r="111" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A111" s="3">
         <v>103</v>
       </c>
@@ -6593,7 +6569,7 @@
       <c r="O111" s="5"/>
       <c r="P111" s="5"/>
     </row>
-    <row r="112" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A112" s="3">
         <v>104</v>
       </c>
@@ -6627,7 +6603,7 @@
       <c r="O112" s="5"/>
       <c r="P112" s="5"/>
     </row>
-    <row r="113" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A113" s="3">
         <v>105</v>
       </c>
@@ -6661,7 +6637,7 @@
       <c r="O113" s="5"/>
       <c r="P113" s="5"/>
     </row>
-    <row r="114" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A114" s="3">
         <v>106</v>
       </c>
@@ -6695,7 +6671,7 @@
       <c r="O114" s="5"/>
       <c r="P114" s="5"/>
     </row>
-    <row r="115" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A115" s="3">
         <v>107</v>
       </c>
@@ -6729,7 +6705,7 @@
       <c r="O115" s="5"/>
       <c r="P115" s="5"/>
     </row>
-    <row r="116" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A116" s="3">
         <v>108</v>
       </c>
@@ -6763,7 +6739,7 @@
       <c r="O116" s="5"/>
       <c r="P116" s="5"/>
     </row>
-    <row r="117" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A117" s="3">
         <v>109</v>
       </c>
@@ -6797,7 +6773,7 @@
       <c r="O117" s="5"/>
       <c r="P117" s="5"/>
     </row>
-    <row r="118" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A118" s="3">
         <v>110</v>
       </c>
@@ -6831,7 +6807,7 @@
       <c r="O118" s="5"/>
       <c r="P118" s="5"/>
     </row>
-    <row r="119" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A119" s="3">
         <v>111</v>
       </c>
@@ -6865,7 +6841,7 @@
       <c r="O119" s="5"/>
       <c r="P119" s="5"/>
     </row>
-    <row r="120" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A120" s="3">
         <v>112</v>
       </c>
@@ -6899,7 +6875,7 @@
       <c r="O120" s="5"/>
       <c r="P120" s="5"/>
     </row>
-    <row r="121" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A121" s="3">
         <v>113</v>
       </c>
@@ -6933,7 +6909,7 @@
       <c r="O121" s="5"/>
       <c r="P121" s="5"/>
     </row>
-    <row r="122" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A122" s="3">
         <v>114</v>
       </c>
@@ -6967,7 +6943,7 @@
       <c r="O122" s="5"/>
       <c r="P122" s="5"/>
     </row>
-    <row r="123" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A123" s="3">
         <v>115</v>
       </c>
@@ -7001,7 +6977,7 @@
       <c r="O123" s="5"/>
       <c r="P123" s="5"/>
     </row>
-    <row r="124" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A124" s="3">
         <v>116</v>
       </c>
@@ -7035,7 +7011,7 @@
       <c r="O124" s="5"/>
       <c r="P124" s="5"/>
     </row>
-    <row r="125" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A125" s="3">
         <v>117</v>
       </c>
@@ -7069,7 +7045,7 @@
       <c r="O125" s="5"/>
       <c r="P125" s="5"/>
     </row>
-    <row r="126" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A126" s="3">
         <v>118</v>
       </c>
@@ -7103,7 +7079,7 @@
       <c r="O126" s="5"/>
       <c r="P126" s="5"/>
     </row>
-    <row r="127" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A127" s="3">
         <v>119</v>
       </c>
@@ -7137,7 +7113,7 @@
       <c r="O127" s="5"/>
       <c r="P127" s="5"/>
     </row>
-    <row r="128" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A128" s="3">
         <v>120</v>
       </c>
@@ -7171,7 +7147,7 @@
       <c r="O128" s="5"/>
       <c r="P128" s="5"/>
     </row>
-    <row r="129" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A129" s="3">
         <v>121</v>
       </c>
@@ -7205,7 +7181,7 @@
       <c r="O129" s="5"/>
       <c r="P129" s="5"/>
     </row>
-    <row r="130" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A130" s="3">
         <v>122</v>
       </c>
@@ -7239,7 +7215,7 @@
       <c r="O130" s="5"/>
       <c r="P130" s="5"/>
     </row>
-    <row r="131" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A131" s="3">
         <v>123</v>
       </c>
@@ -7273,7 +7249,7 @@
       <c r="O131" s="5"/>
       <c r="P131" s="5"/>
     </row>
-    <row r="132" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A132" s="3">
         <v>124</v>
       </c>
@@ -7307,7 +7283,7 @@
       <c r="O132" s="5"/>
       <c r="P132" s="5"/>
     </row>
-    <row r="133" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A133" s="3">
         <v>125</v>
       </c>
@@ -7341,7 +7317,7 @@
       <c r="O133" s="5"/>
       <c r="P133" s="5"/>
     </row>
-    <row r="134" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A134" s="3">
         <v>126</v>
       </c>
@@ -7375,7 +7351,7 @@
       <c r="O134" s="5"/>
       <c r="P134" s="5"/>
     </row>
-    <row r="135" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A135" s="3">
         <v>127</v>
       </c>
@@ -7409,7 +7385,7 @@
       <c r="O135" s="5"/>
       <c r="P135" s="5"/>
     </row>
-    <row r="136" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A136" s="3">
         <v>128</v>
       </c>
@@ -7443,7 +7419,7 @@
       <c r="O136" s="5"/>
       <c r="P136" s="5"/>
     </row>
-    <row r="137" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A137" s="3">
         <v>129</v>
       </c>
@@ -7477,7 +7453,7 @@
       <c r="O137" s="5"/>
       <c r="P137" s="5"/>
     </row>
-    <row r="138" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A138" s="3">
         <v>130</v>
       </c>
@@ -7511,7 +7487,7 @@
       <c r="O138" s="5"/>
       <c r="P138" s="5"/>
     </row>
-    <row r="139" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A139" s="3">
         <v>131</v>
       </c>
@@ -7545,7 +7521,7 @@
       <c r="O139" s="5"/>
       <c r="P139" s="5"/>
     </row>
-    <row r="140" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A140" s="3">
         <v>132</v>
       </c>
@@ -7579,7 +7555,7 @@
       <c r="O140" s="5"/>
       <c r="P140" s="5"/>
     </row>
-    <row r="141" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A141" s="3">
         <v>133</v>
       </c>
@@ -7613,7 +7589,7 @@
       <c r="O141" s="5"/>
       <c r="P141" s="5"/>
     </row>
-    <row r="142" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A142" s="3">
         <v>134</v>
       </c>
@@ -7647,7 +7623,7 @@
       <c r="O142" s="5"/>
       <c r="P142" s="5"/>
     </row>
-    <row r="143" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A143" s="3">
         <v>135</v>
       </c>
@@ -7681,7 +7657,7 @@
       <c r="O143" s="5"/>
       <c r="P143" s="5"/>
     </row>
-    <row r="144" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A144" s="3">
         <v>136</v>
       </c>
@@ -7715,7 +7691,7 @@
       <c r="O144" s="5"/>
       <c r="P144" s="5"/>
     </row>
-    <row r="145" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A145" s="3">
         <v>137</v>
       </c>
@@ -7749,7 +7725,7 @@
       <c r="O145" s="5"/>
       <c r="P145" s="5"/>
     </row>
-    <row r="146" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A146" s="3">
         <v>138</v>
       </c>
@@ -7783,7 +7759,7 @@
       <c r="O146" s="5"/>
       <c r="P146" s="5"/>
     </row>
-    <row r="147" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A147" s="3">
         <v>139</v>
       </c>
@@ -7817,7 +7793,7 @@
       <c r="O147" s="5"/>
       <c r="P147" s="5"/>
     </row>
-    <row r="148" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A148" s="3">
         <v>140</v>
       </c>
@@ -7851,7 +7827,7 @@
       <c r="O148" s="5"/>
       <c r="P148" s="5"/>
     </row>
-    <row r="149" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A149" s="3">
         <v>141</v>
       </c>
@@ -7885,7 +7861,7 @@
       <c r="O149" s="5"/>
       <c r="P149" s="5"/>
     </row>
-    <row r="150" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A150" s="3">
         <v>142</v>
       </c>
@@ -7919,7 +7895,7 @@
       <c r="O150" s="5"/>
       <c r="P150" s="5"/>
     </row>
-    <row r="151" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A151" s="3">
         <v>143</v>
       </c>
@@ -7953,7 +7929,7 @@
       <c r="O151" s="5"/>
       <c r="P151" s="5"/>
     </row>
-    <row r="152" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A152" s="3">
         <v>144</v>
       </c>
@@ -7987,7 +7963,7 @@
       <c r="O152" s="5"/>
       <c r="P152" s="5"/>
     </row>
-    <row r="153" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A153" s="3">
         <v>145</v>
       </c>
@@ -8021,7 +7997,7 @@
       <c r="O153" s="5"/>
       <c r="P153" s="5"/>
     </row>
-    <row r="154" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A154" s="3">
         <v>146</v>
       </c>
@@ -8055,7 +8031,7 @@
       <c r="O154" s="5"/>
       <c r="P154" s="5"/>
     </row>
-    <row r="155" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A155" s="3">
         <v>147</v>
       </c>
@@ -8089,7 +8065,7 @@
       <c r="O155" s="5"/>
       <c r="P155" s="5"/>
     </row>
-    <row r="156" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A156" s="3">
         <v>148</v>
       </c>
@@ -8123,7 +8099,7 @@
       <c r="O156" s="5"/>
       <c r="P156" s="5"/>
     </row>
-    <row r="157" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A157" s="3">
         <v>149</v>
       </c>
@@ -8157,7 +8133,7 @@
       <c r="O157" s="5"/>
       <c r="P157" s="5"/>
     </row>
-    <row r="158" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A158" s="3">
         <v>150</v>
       </c>
@@ -8191,7 +8167,7 @@
       <c r="O158" s="5"/>
       <c r="P158" s="5"/>
     </row>
-    <row r="159" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A159" s="3">
         <v>151</v>
       </c>
@@ -8225,7 +8201,7 @@
       <c r="O159" s="5"/>
       <c r="P159" s="5"/>
     </row>
-    <row r="160" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A160" s="3">
         <v>152</v>
       </c>
@@ -8259,7 +8235,7 @@
       <c r="O160" s="5"/>
       <c r="P160" s="5"/>
     </row>
-    <row r="161" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A161" s="3">
         <v>153</v>
       </c>
@@ -8293,7 +8269,7 @@
       <c r="O161" s="5"/>
       <c r="P161" s="5"/>
     </row>
-    <row r="162" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A162" s="3">
         <v>154</v>
       </c>
@@ -8327,7 +8303,7 @@
       <c r="O162" s="5"/>
       <c r="P162" s="5"/>
     </row>
-    <row r="163" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A163" s="3">
         <v>155</v>
       </c>
@@ -8361,7 +8337,7 @@
       <c r="O163" s="5"/>
       <c r="P163" s="5"/>
     </row>
-    <row r="164" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A164" s="3">
         <v>156</v>
       </c>
@@ -8395,7 +8371,7 @@
       <c r="O164" s="5"/>
       <c r="P164" s="5"/>
     </row>
-    <row r="165" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A165" s="3">
         <v>157</v>
       </c>
@@ -8429,7 +8405,7 @@
       <c r="O165" s="5"/>
       <c r="P165" s="5"/>
     </row>
-    <row r="166" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A166" s="3">
         <v>158</v>
       </c>
@@ -8463,7 +8439,7 @@
       <c r="O166" s="5"/>
       <c r="P166" s="5"/>
     </row>
-    <row r="167" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A167" s="3">
         <v>159</v>
       </c>
@@ -8497,7 +8473,7 @@
       <c r="O167" s="5"/>
       <c r="P167" s="5"/>
     </row>
-    <row r="168" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A168" s="3">
         <v>160</v>
       </c>
@@ -8531,7 +8507,7 @@
       <c r="O168" s="5"/>
       <c r="P168" s="5"/>
     </row>
-    <row r="169" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A169" s="3">
         <v>161</v>
       </c>
@@ -8565,7 +8541,7 @@
       <c r="O169" s="5"/>
       <c r="P169" s="5"/>
     </row>
-    <row r="170" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A170" s="3">
         <v>162</v>
       </c>
@@ -8599,7 +8575,7 @@
       <c r="O170" s="5"/>
       <c r="P170" s="5"/>
     </row>
-    <row r="171" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A171" s="3">
         <v>163</v>
       </c>
@@ -8633,7 +8609,7 @@
       <c r="O171" s="5"/>
       <c r="P171" s="5"/>
     </row>
-    <row r="172" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A172" s="3">
         <v>164</v>
       </c>
@@ -8667,7 +8643,7 @@
       <c r="O172" s="5"/>
       <c r="P172" s="5"/>
     </row>
-    <row r="173" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A173" s="3">
         <v>165</v>
       </c>
@@ -8701,7 +8677,7 @@
       <c r="O173" s="5"/>
       <c r="P173" s="5"/>
     </row>
-    <row r="174" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A174" s="3">
         <v>166</v>
       </c>
@@ -8735,7 +8711,7 @@
       <c r="O174" s="5"/>
       <c r="P174" s="5"/>
     </row>
-    <row r="175" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A175" s="3">
         <v>167</v>
       </c>
@@ -8769,7 +8745,7 @@
       <c r="O175" s="5"/>
       <c r="P175" s="5"/>
     </row>
-    <row r="176" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A176" s="3">
         <v>168</v>
       </c>
@@ -8803,7 +8779,7 @@
       <c r="O176" s="5"/>
       <c r="P176" s="5"/>
     </row>
-    <row r="177" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A177" s="3">
         <v>169</v>
       </c>
@@ -8837,7 +8813,7 @@
       <c r="O177" s="5"/>
       <c r="P177" s="5"/>
     </row>
-    <row r="178" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A178" s="3">
         <v>170</v>
       </c>
@@ -8871,7 +8847,7 @@
       <c r="O178" s="5"/>
       <c r="P178" s="5"/>
     </row>
-    <row r="179" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A179" s="3">
         <v>171</v>
       </c>
@@ -8905,7 +8881,7 @@
       <c r="O179" s="5"/>
       <c r="P179" s="5"/>
     </row>
-    <row r="180" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A180" s="3">
         <v>172</v>
       </c>
@@ -8939,7 +8915,7 @@
       <c r="O180" s="5"/>
       <c r="P180" s="5"/>
     </row>
-    <row r="181" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A181" s="3">
         <v>173</v>
       </c>
@@ -8973,7 +8949,7 @@
       <c r="O181" s="5"/>
       <c r="P181" s="5"/>
     </row>
-    <row r="182" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A182" s="3">
         <v>174</v>
       </c>
@@ -9007,7 +8983,7 @@
       <c r="O182" s="5"/>
       <c r="P182" s="5"/>
     </row>
-    <row r="183" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A183" s="3">
         <v>175</v>
       </c>
@@ -9041,7 +9017,7 @@
       <c r="O183" s="5"/>
       <c r="P183" s="5"/>
     </row>
-    <row r="184" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A184" s="3">
         <v>176</v>
       </c>
@@ -9075,7 +9051,7 @@
       <c r="O184" s="5"/>
       <c r="P184" s="5"/>
     </row>
-    <row r="185" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A185" s="3">
         <v>177</v>
       </c>
@@ -9109,7 +9085,7 @@
       <c r="O185" s="5"/>
       <c r="P185" s="5"/>
     </row>
-    <row r="186" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A186" s="3">
         <v>178</v>
       </c>
@@ -9143,7 +9119,7 @@
       <c r="O186" s="5"/>
       <c r="P186" s="5"/>
     </row>
-    <row r="187" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A187" s="3">
         <v>179</v>
       </c>
@@ -9177,7 +9153,7 @@
       <c r="O187" s="5"/>
       <c r="P187" s="5"/>
     </row>
-    <row r="188" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A188" s="3">
         <v>180</v>
       </c>
@@ -9211,7 +9187,7 @@
       <c r="O188" s="5"/>
       <c r="P188" s="5"/>
     </row>
-    <row r="189" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A189" s="3">
         <v>181</v>
       </c>
@@ -9245,7 +9221,7 @@
       <c r="O189" s="5"/>
       <c r="P189" s="5"/>
     </row>
-    <row r="190" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A190" s="3">
         <v>182</v>
       </c>
@@ -9279,7 +9255,7 @@
       <c r="O190" s="5"/>
       <c r="P190" s="5"/>
     </row>
-    <row r="191" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A191" s="3">
         <v>183</v>
       </c>
@@ -9313,7 +9289,7 @@
       <c r="O191" s="5"/>
       <c r="P191" s="5"/>
     </row>
-    <row r="192" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A192" s="3">
         <v>184</v>
       </c>
@@ -9347,7 +9323,7 @@
       <c r="O192" s="5"/>
       <c r="P192" s="5"/>
     </row>
-    <row r="193" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A193" s="3">
         <v>185</v>
       </c>
@@ -9381,7 +9357,7 @@
       <c r="O193" s="5"/>
       <c r="P193" s="5"/>
     </row>
-    <row r="194" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A194" s="3">
         <v>186</v>
       </c>
@@ -9415,7 +9391,7 @@
       <c r="O194" s="5"/>
       <c r="P194" s="5"/>
     </row>
-    <row r="195" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A195" s="3">
         <v>187</v>
       </c>
@@ -9449,7 +9425,7 @@
       <c r="O195" s="5"/>
       <c r="P195" s="5"/>
     </row>
-    <row r="196" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A196" s="3">
         <v>188</v>
       </c>
@@ -9483,7 +9459,7 @@
       <c r="O196" s="5"/>
       <c r="P196" s="5"/>
     </row>
-    <row r="197" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A197" s="3">
         <v>189</v>
       </c>
@@ -9517,7 +9493,7 @@
       <c r="O197" s="5"/>
       <c r="P197" s="5"/>
     </row>
-    <row r="198" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A198" s="3">
         <v>190</v>
       </c>
@@ -9551,7 +9527,7 @@
       <c r="O198" s="5"/>
       <c r="P198" s="5"/>
     </row>
-    <row r="199" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A199" s="3">
         <v>191</v>
       </c>
@@ -9585,7 +9561,7 @@
       <c r="O199" s="5"/>
       <c r="P199" s="5"/>
     </row>
-    <row r="200" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A200" s="3">
         <v>192</v>
       </c>
@@ -9619,7 +9595,7 @@
       <c r="O200" s="5"/>
       <c r="P200" s="5"/>
     </row>
-    <row r="201" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A201" s="3">
         <v>193</v>
       </c>
@@ -9653,7 +9629,7 @@
       <c r="O201" s="5"/>
       <c r="P201" s="5"/>
     </row>
-    <row r="202" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A202" s="3">
         <v>194</v>
       </c>
@@ -9687,7 +9663,7 @@
       <c r="O202" s="5"/>
       <c r="P202" s="5"/>
     </row>
-    <row r="203" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A203" s="3">
         <v>195</v>
       </c>
@@ -9721,7 +9697,7 @@
       <c r="O203" s="5"/>
       <c r="P203" s="5"/>
     </row>
-    <row r="204" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A204" s="3">
         <v>196</v>
       </c>
@@ -9755,7 +9731,7 @@
       <c r="O204" s="5"/>
       <c r="P204" s="5"/>
     </row>
-    <row r="205" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A205" s="3">
         <v>197</v>
       </c>
@@ -9789,7 +9765,7 @@
       <c r="O205" s="5"/>
       <c r="P205" s="5"/>
     </row>
-    <row r="206" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A206" s="3">
         <v>198</v>
       </c>
@@ -9823,7 +9799,7 @@
       <c r="O206" s="5"/>
       <c r="P206" s="5"/>
     </row>
-    <row r="207" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A207" s="3">
         <v>199</v>
       </c>
@@ -9857,7 +9833,7 @@
       <c r="O207" s="5"/>
       <c r="P207" s="5"/>
     </row>
-    <row r="208" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A208" s="3">
         <v>200</v>
       </c>
@@ -9891,7 +9867,7 @@
       <c r="O208" s="5"/>
       <c r="P208" s="5"/>
     </row>
-    <row r="209" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A209" s="3">
         <v>201</v>
       </c>
@@ -9925,7 +9901,7 @@
       <c r="O209" s="5"/>
       <c r="P209" s="5"/>
     </row>
-    <row r="210" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A210" s="3">
         <v>202</v>
       </c>
@@ -9959,7 +9935,7 @@
       <c r="O210" s="5"/>
       <c r="P210" s="5"/>
     </row>
-    <row r="211" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A211" s="3">
         <v>203</v>
       </c>
@@ -9993,7 +9969,7 @@
       <c r="O211" s="5"/>
       <c r="P211" s="5"/>
     </row>
-    <row r="212" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A212" s="3">
         <v>204</v>
       </c>
@@ -10027,7 +10003,7 @@
       <c r="O212" s="5"/>
       <c r="P212" s="5"/>
     </row>
-    <row r="213" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A213" s="3">
         <v>205</v>
       </c>
@@ -10061,7 +10037,7 @@
       <c r="O213" s="5"/>
       <c r="P213" s="5"/>
     </row>
-    <row r="214" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A214" s="3">
         <v>206</v>
       </c>
@@ -10125,26 +10101,26 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{48F26D4F-7731-4458-841B-32B80A9F847D}">
   <dimension ref="B4:Q36"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="5.28515625" customWidth="1"/>
-    <col min="4" max="4" width="28.140625" customWidth="1"/>
-    <col min="5" max="5" width="12.7109375" customWidth="1"/>
-    <col min="6" max="6" width="25.140625" customWidth="1"/>
-    <col min="7" max="7" width="26.140625" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" customWidth="1"/>
-    <col min="9" max="9" width="16.85546875" customWidth="1"/>
-    <col min="10" max="10" width="24.42578125" customWidth="1"/>
-    <col min="11" max="11" width="26.5703125" customWidth="1"/>
-    <col min="12" max="12" width="14.42578125" customWidth="1"/>
-    <col min="13" max="13" width="12.5703125" customWidth="1"/>
-    <col min="14" max="14" width="20.85546875" customWidth="1"/>
-    <col min="15" max="15" width="18.85546875" customWidth="1"/>
-    <col min="16" max="16" width="13.28515625" customWidth="1"/>
-    <col min="17" max="17" width="20.28515625" customWidth="1"/>
+    <col min="2" max="2" width="5.26953125" customWidth="1"/>
+    <col min="4" max="4" width="28.1796875" customWidth="1"/>
+    <col min="5" max="5" width="12.7265625" customWidth="1"/>
+    <col min="6" max="6" width="25.1796875" customWidth="1"/>
+    <col min="7" max="7" width="26.1796875" customWidth="1"/>
+    <col min="8" max="8" width="14.81640625" customWidth="1"/>
+    <col min="9" max="9" width="16.81640625" customWidth="1"/>
+    <col min="10" max="10" width="24.453125" customWidth="1"/>
+    <col min="11" max="11" width="26.54296875" customWidth="1"/>
+    <col min="12" max="12" width="14.453125" customWidth="1"/>
+    <col min="13" max="13" width="12.54296875" customWidth="1"/>
+    <col min="14" max="14" width="20.81640625" customWidth="1"/>
+    <col min="15" max="15" width="18.81640625" customWidth="1"/>
+    <col min="16" max="16" width="13.26953125" customWidth="1"/>
+    <col min="17" max="17" width="20.26953125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="4" spans="2:17" ht="24" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:17" ht="23" x14ac:dyDescent="0.35">
       <c r="B4" s="14" t="s">
         <v>2</v>
       </c>
@@ -10185,7 +10161,7 @@
         <v>8</v>
       </c>
       <c r="O4" s="14" t="s">
-        <v>791</v>
+        <v>783</v>
       </c>
       <c r="P4" s="14" t="s">
         <v>13</v>
@@ -10194,8 +10170,8 @@
         <v>14</v>
       </c>
     </row>
-    <row r="5" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B5" s="32">
+    <row r="5" spans="2:17" x14ac:dyDescent="0.35">
+      <c r="B5" s="30">
         <v>1</v>
       </c>
       <c r="C5" s="17" t="s">
@@ -10216,7 +10192,7 @@
       <c r="H5" s="19" t="s">
         <v>648</v>
       </c>
-      <c r="I5" s="30" t="s">
+      <c r="I5" s="28" t="s">
         <v>713</v>
       </c>
       <c r="J5" s="18" t="s">
@@ -10235,15 +10211,15 @@
         <v>672</v>
       </c>
       <c r="O5" s="23" t="s">
-        <v>792</v>
+        <v>784</v>
       </c>
       <c r="P5" s="16"/>
       <c r="Q5" s="24" t="s">
         <v>684</v>
       </c>
     </row>
-    <row r="6" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B6" s="32">
+    <row r="6" spans="2:17" x14ac:dyDescent="0.35">
+      <c r="B6" s="30">
         <v>2</v>
       </c>
       <c r="C6" s="17" t="s">
@@ -10283,15 +10259,15 @@
         <v>673</v>
       </c>
       <c r="O6" s="23" t="s">
-        <v>792</v>
+        <v>784</v>
       </c>
       <c r="P6" s="16"/>
       <c r="Q6" s="24" t="s">
         <v>685</v>
       </c>
     </row>
-    <row r="7" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B7" s="32">
+    <row r="7" spans="2:17" x14ac:dyDescent="0.35">
+      <c r="B7" s="30">
         <v>3</v>
       </c>
       <c r="C7" s="17" t="s">
@@ -10331,15 +10307,15 @@
         <v>674</v>
       </c>
       <c r="O7" s="23" t="s">
-        <v>792</v>
+        <v>784</v>
       </c>
       <c r="P7" s="16"/>
       <c r="Q7" s="24" t="s">
         <v>686</v>
       </c>
     </row>
-    <row r="8" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B8" s="32">
+    <row r="8" spans="2:17" x14ac:dyDescent="0.35">
+      <c r="B8" s="30">
         <v>4</v>
       </c>
       <c r="C8" s="17" t="s">
@@ -10379,15 +10355,15 @@
         <v>675</v>
       </c>
       <c r="O8" s="23" t="s">
-        <v>793</v>
+        <v>785</v>
       </c>
       <c r="P8" s="16"/>
       <c r="Q8" s="24" t="s">
         <v>687</v>
       </c>
     </row>
-    <row r="9" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B9" s="32">
+    <row r="9" spans="2:17" x14ac:dyDescent="0.35">
+      <c r="B9" s="30">
         <v>5</v>
       </c>
       <c r="C9" s="17" t="s">
@@ -10427,15 +10403,15 @@
         <v>676</v>
       </c>
       <c r="O9" s="23" t="s">
-        <v>792</v>
+        <v>784</v>
       </c>
       <c r="P9" s="16"/>
       <c r="Q9" s="24" t="s">
         <v>688</v>
       </c>
     </row>
-    <row r="10" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B10" s="32">
+    <row r="10" spans="2:17" x14ac:dyDescent="0.35">
+      <c r="B10" s="30">
         <v>6</v>
       </c>
       <c r="C10" s="17" t="s">
@@ -10475,15 +10451,15 @@
         <v>677</v>
       </c>
       <c r="O10" s="23" t="s">
-        <v>792</v>
+        <v>784</v>
       </c>
       <c r="P10" s="16"/>
       <c r="Q10" s="24" t="s">
         <v>684</v>
       </c>
     </row>
-    <row r="11" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B11" s="32">
+    <row r="11" spans="2:17" x14ac:dyDescent="0.35">
+      <c r="B11" s="30">
         <v>7</v>
       </c>
       <c r="C11" s="17" t="s">
@@ -10523,15 +10499,15 @@
         <v>678</v>
       </c>
       <c r="O11" s="23" t="s">
-        <v>792</v>
+        <v>784</v>
       </c>
       <c r="P11" s="16"/>
       <c r="Q11" s="24" t="s">
         <v>689</v>
       </c>
     </row>
-    <row r="12" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B12" s="32">
+    <row r="12" spans="2:17" x14ac:dyDescent="0.35">
+      <c r="B12" s="30">
         <v>8</v>
       </c>
       <c r="C12" s="17" t="s">
@@ -10571,15 +10547,15 @@
         <v>679</v>
       </c>
       <c r="O12" s="23" t="s">
-        <v>792</v>
+        <v>784</v>
       </c>
       <c r="P12" s="16"/>
       <c r="Q12" s="24" t="s">
         <v>688</v>
       </c>
     </row>
-    <row r="13" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B13" s="32">
+    <row r="13" spans="2:17" x14ac:dyDescent="0.35">
+      <c r="B13" s="30">
         <v>9</v>
       </c>
       <c r="C13" s="17" t="s">
@@ -10619,15 +10595,15 @@
         <v>680</v>
       </c>
       <c r="O13" s="23" t="s">
-        <v>792</v>
+        <v>784</v>
       </c>
       <c r="P13" s="16"/>
       <c r="Q13" s="24" t="s">
         <v>690</v>
       </c>
     </row>
-    <row r="14" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B14" s="32">
+    <row r="14" spans="2:17" x14ac:dyDescent="0.35">
+      <c r="B14" s="30">
         <v>10</v>
       </c>
       <c r="C14" s="17" t="s">
@@ -10667,15 +10643,15 @@
         <v>681</v>
       </c>
       <c r="O14" s="23" t="s">
-        <v>792</v>
+        <v>784</v>
       </c>
       <c r="P14" s="16"/>
       <c r="Q14" s="24" t="s">
         <v>690</v>
       </c>
     </row>
-    <row r="15" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B15" s="32">
+    <row r="15" spans="2:17" x14ac:dyDescent="0.35">
+      <c r="B15" s="30">
         <v>11</v>
       </c>
       <c r="C15" s="17" t="s">
@@ -10715,15 +10691,15 @@
         <v>682</v>
       </c>
       <c r="O15" s="23" t="s">
-        <v>792</v>
+        <v>784</v>
       </c>
       <c r="P15" s="16"/>
       <c r="Q15" s="24" t="s">
         <v>684</v>
       </c>
     </row>
-    <row r="16" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B16" s="32">
+    <row r="16" spans="2:17" x14ac:dyDescent="0.35">
+      <c r="B16" s="30">
         <v>12</v>
       </c>
       <c r="C16" s="17" t="s">
@@ -10763,15 +10739,15 @@
         <v>683</v>
       </c>
       <c r="O16" s="23" t="s">
-        <v>792</v>
+        <v>784</v>
       </c>
       <c r="P16" s="16"/>
       <c r="Q16" s="24" t="s">
         <v>684</v>
       </c>
     </row>
-    <row r="17" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B17" s="32">
+    <row r="17" spans="2:17" x14ac:dyDescent="0.35">
+      <c r="B17" s="30">
         <v>13</v>
       </c>
       <c r="C17" s="17" t="s">
@@ -10811,15 +10787,15 @@
         <v>693</v>
       </c>
       <c r="O17" s="23" t="s">
-        <v>792</v>
+        <v>784</v>
       </c>
       <c r="P17" s="16"/>
       <c r="Q17" s="24" t="s">
         <v>704</v>
       </c>
     </row>
-    <row r="18" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B18" s="32">
+    <row r="18" spans="2:17" x14ac:dyDescent="0.35">
+      <c r="B18" s="30">
         <v>14</v>
       </c>
       <c r="C18" s="17" t="s">
@@ -10859,15 +10835,15 @@
         <v>694</v>
       </c>
       <c r="O18" s="23" t="s">
-        <v>792</v>
+        <v>784</v>
       </c>
       <c r="P18" s="16"/>
       <c r="Q18" s="24" t="s">
         <v>684</v>
       </c>
     </row>
-    <row r="19" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B19" s="32">
+    <row r="19" spans="2:17" x14ac:dyDescent="0.35">
+      <c r="B19" s="30">
         <v>15</v>
       </c>
       <c r="C19" s="17" t="s">
@@ -10907,15 +10883,15 @@
         <v>695</v>
       </c>
       <c r="O19" s="23" t="s">
-        <v>792</v>
+        <v>784</v>
       </c>
       <c r="P19" s="16"/>
       <c r="Q19" s="24" t="s">
         <v>687</v>
       </c>
     </row>
-    <row r="20" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B20" s="32">
+    <row r="20" spans="2:17" x14ac:dyDescent="0.35">
+      <c r="B20" s="30">
         <v>16</v>
       </c>
       <c r="C20" s="17" t="s">
@@ -10955,15 +10931,15 @@
         <v>696</v>
       </c>
       <c r="O20" s="23" t="s">
-        <v>792</v>
+        <v>784</v>
       </c>
       <c r="P20" s="16"/>
       <c r="Q20" s="24" t="s">
         <v>684</v>
       </c>
     </row>
-    <row r="21" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B21" s="32">
+    <row r="21" spans="2:17" x14ac:dyDescent="0.35">
+      <c r="B21" s="30">
         <v>17</v>
       </c>
       <c r="C21" s="17" t="s">
@@ -11003,15 +10979,15 @@
         <v>697</v>
       </c>
       <c r="O21" s="23" t="s">
-        <v>792</v>
+        <v>784</v>
       </c>
       <c r="P21" s="16"/>
       <c r="Q21" s="24" t="s">
         <v>684</v>
       </c>
     </row>
-    <row r="22" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B22" s="32">
+    <row r="22" spans="2:17" x14ac:dyDescent="0.35">
+      <c r="B22" s="30">
         <v>18</v>
       </c>
       <c r="C22" s="17" t="s">
@@ -11051,15 +11027,15 @@
         <v>698</v>
       </c>
       <c r="O22" s="23" t="s">
-        <v>792</v>
+        <v>784</v>
       </c>
       <c r="P22" s="16"/>
       <c r="Q22" s="24" t="s">
         <v>690</v>
       </c>
     </row>
-    <row r="23" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B23" s="32">
+    <row r="23" spans="2:17" x14ac:dyDescent="0.35">
+      <c r="B23" s="30">
         <v>19</v>
       </c>
       <c r="C23" s="17" t="s">
@@ -11099,15 +11075,15 @@
         <v>699</v>
       </c>
       <c r="O23" s="23" t="s">
-        <v>792</v>
+        <v>784</v>
       </c>
       <c r="P23" s="16"/>
       <c r="Q23" s="24" t="s">
         <v>690</v>
       </c>
     </row>
-    <row r="24" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B24" s="32">
+    <row r="24" spans="2:17" x14ac:dyDescent="0.35">
+      <c r="B24" s="30">
         <v>20</v>
       </c>
       <c r="C24" s="17" t="s">
@@ -11147,15 +11123,15 @@
         <v>700</v>
       </c>
       <c r="O24" s="23" t="s">
-        <v>792</v>
+        <v>784</v>
       </c>
       <c r="P24" s="16"/>
       <c r="Q24" s="24" t="s">
         <v>690</v>
       </c>
     </row>
-    <row r="25" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B25" s="32">
+    <row r="25" spans="2:17" x14ac:dyDescent="0.35">
+      <c r="B25" s="30">
         <v>21</v>
       </c>
       <c r="C25" s="17" t="s">
@@ -11195,15 +11171,15 @@
         <v>701</v>
       </c>
       <c r="O25" s="23" t="s">
-        <v>792</v>
+        <v>784</v>
       </c>
       <c r="P25" s="16"/>
       <c r="Q25" s="24" t="s">
         <v>690</v>
       </c>
     </row>
-    <row r="26" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B26" s="32">
+    <row r="26" spans="2:17" x14ac:dyDescent="0.35">
+      <c r="B26" s="30">
         <v>22</v>
       </c>
       <c r="C26" s="17" t="s">
@@ -11243,15 +11219,15 @@
         <v>702</v>
       </c>
       <c r="O26" s="23" t="s">
-        <v>792</v>
+        <v>784</v>
       </c>
       <c r="P26" s="16"/>
       <c r="Q26" s="24" t="s">
         <v>690</v>
       </c>
     </row>
-    <row r="27" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B27" s="32">
+    <row r="27" spans="2:17" x14ac:dyDescent="0.35">
+      <c r="B27" s="30">
         <v>23</v>
       </c>
       <c r="C27" s="17" t="s">
@@ -11291,15 +11267,15 @@
         <v>695</v>
       </c>
       <c r="O27" s="23" t="s">
-        <v>792</v>
+        <v>784</v>
       </c>
       <c r="P27" s="16"/>
       <c r="Q27" s="24" t="s">
         <v>688</v>
       </c>
     </row>
-    <row r="28" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B28" s="32">
+    <row r="28" spans="2:17" x14ac:dyDescent="0.35">
+      <c r="B28" s="30">
         <v>24</v>
       </c>
       <c r="C28" s="17" t="s">
@@ -11339,19 +11315,19 @@
         <v>703</v>
       </c>
       <c r="O28" s="23" t="s">
-        <v>792</v>
+        <v>784</v>
       </c>
       <c r="P28" s="16"/>
       <c r="Q28" s="24" t="s">
         <v>688</v>
       </c>
     </row>
-    <row r="29" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="29" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B29" s="27">
         <v>25</v>
       </c>
-      <c r="C29" s="17" t="s">
-        <v>783</v>
+      <c r="C29" s="17">
+        <v>96050450</v>
       </c>
       <c r="D29" s="17" t="s">
         <v>355</v>
@@ -11362,13 +11338,13 @@
       <c r="F29" s="18" t="s">
         <v>356</v>
       </c>
-      <c r="G29" s="33" t="s">
+      <c r="G29" s="31" t="s">
         <v>357</v>
       </c>
-      <c r="H29" s="33" t="s">
+      <c r="H29" s="31" t="s">
         <v>744</v>
       </c>
-      <c r="I29" s="31" t="s">
+      <c r="I29" s="29" t="s">
         <v>751</v>
       </c>
       <c r="J29" s="18" t="s">
@@ -11387,36 +11363,36 @@
         <v>705</v>
       </c>
       <c r="O29" s="23" t="s">
-        <v>792</v>
+        <v>784</v>
       </c>
       <c r="P29" s="16"/>
       <c r="Q29" s="24" t="s">
         <v>690</v>
       </c>
     </row>
-    <row r="30" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="30" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B30" s="27">
         <v>26</v>
       </c>
-      <c r="C30" s="17" t="s">
-        <v>784</v>
+      <c r="C30" s="17">
+        <v>96050451</v>
       </c>
       <c r="D30" s="17" t="s">
         <v>358</v>
       </c>
-      <c r="E30" s="32" t="s">
+      <c r="E30" s="30" t="s">
         <v>16</v>
       </c>
       <c r="F30" s="18" t="s">
         <v>359</v>
       </c>
-      <c r="G30" s="33" t="s">
+      <c r="G30" s="31" t="s">
         <v>360</v>
       </c>
-      <c r="H30" s="33" t="s">
+      <c r="H30" s="31" t="s">
         <v>648</v>
       </c>
-      <c r="I30" s="31" t="s">
+      <c r="I30" s="29" t="s">
         <v>752</v>
       </c>
       <c r="J30" s="18" t="s">
@@ -11435,36 +11411,36 @@
         <v>706</v>
       </c>
       <c r="O30" s="23" t="s">
-        <v>792</v>
+        <v>784</v>
       </c>
       <c r="P30" s="16"/>
       <c r="Q30" s="24" t="s">
         <v>690</v>
       </c>
     </row>
-    <row r="31" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="31" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B31" s="27">
         <v>27</v>
       </c>
-      <c r="C31" s="17" t="s">
-        <v>785</v>
+      <c r="C31" s="17">
+        <v>96050452</v>
       </c>
       <c r="D31" s="17" t="s">
         <v>361</v>
       </c>
-      <c r="E31" s="32" t="s">
+      <c r="E31" s="30" t="s">
         <v>16</v>
       </c>
       <c r="F31" s="18" t="s">
         <v>362</v>
       </c>
-      <c r="G31" s="33" t="s">
+      <c r="G31" s="31" t="s">
         <v>363</v>
       </c>
-      <c r="H31" s="33" t="s">
+      <c r="H31" s="31" t="s">
         <v>648</v>
       </c>
-      <c r="I31" s="31" t="s">
+      <c r="I31" s="29" t="s">
         <v>753</v>
       </c>
       <c r="J31" s="18" t="s">
@@ -11483,36 +11459,36 @@
         <v>707</v>
       </c>
       <c r="O31" s="23" t="s">
-        <v>792</v>
+        <v>784</v>
       </c>
       <c r="P31" s="16"/>
       <c r="Q31" s="24" t="s">
         <v>688</v>
       </c>
     </row>
-    <row r="32" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="32" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B32" s="27">
         <v>28</v>
       </c>
-      <c r="C32" s="17" t="s">
-        <v>786</v>
+      <c r="C32" s="17">
+        <v>96050453</v>
       </c>
       <c r="D32" s="17" t="s">
         <v>364</v>
       </c>
-      <c r="E32" s="32" t="s">
+      <c r="E32" s="30" t="s">
         <v>17</v>
       </c>
       <c r="F32" s="18" t="s">
         <v>365</v>
       </c>
-      <c r="G32" s="33" t="s">
+      <c r="G32" s="31" t="s">
         <v>366</v>
       </c>
-      <c r="H32" s="33" t="s">
+      <c r="H32" s="31" t="s">
         <v>648</v>
       </c>
-      <c r="I32" s="31" t="s">
+      <c r="I32" s="29" t="s">
         <v>754</v>
       </c>
       <c r="J32" s="18" t="s">
@@ -11531,36 +11507,36 @@
         <v>708</v>
       </c>
       <c r="O32" s="23" t="s">
-        <v>792</v>
+        <v>784</v>
       </c>
       <c r="P32" s="16"/>
       <c r="Q32" s="24" t="s">
         <v>688</v>
       </c>
     </row>
-    <row r="33" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="33" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B33" s="27">
         <v>29</v>
       </c>
-      <c r="C33" s="17" t="s">
-        <v>787</v>
+      <c r="C33" s="17">
+        <v>96050457</v>
       </c>
       <c r="D33" s="17" t="s">
         <v>373</v>
       </c>
-      <c r="E33" s="32" t="s">
+      <c r="E33" s="30" t="s">
         <v>16</v>
       </c>
       <c r="F33" s="18" t="s">
         <v>374</v>
       </c>
-      <c r="G33" s="33" t="s">
+      <c r="G33" s="31" t="s">
         <v>375</v>
       </c>
-      <c r="H33" s="33" t="s">
+      <c r="H33" s="31" t="s">
         <v>648</v>
       </c>
-      <c r="I33" s="31" t="s">
+      <c r="I33" s="29" t="s">
         <v>755</v>
       </c>
       <c r="J33" s="18" t="s">
@@ -11579,36 +11555,36 @@
         <v>709</v>
       </c>
       <c r="O33" s="23" t="s">
-        <v>792</v>
+        <v>784</v>
       </c>
       <c r="P33" s="16"/>
       <c r="Q33" s="24" t="s">
         <v>688</v>
       </c>
     </row>
-    <row r="34" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="34" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B34" s="27">
         <v>30</v>
       </c>
-      <c r="C34" s="17" t="s">
-        <v>788</v>
+      <c r="C34" s="17">
+        <v>96050458</v>
       </c>
       <c r="D34" s="17" t="s">
         <v>376</v>
       </c>
-      <c r="E34" s="32" t="s">
+      <c r="E34" s="30" t="s">
         <v>16</v>
       </c>
       <c r="F34" s="18" t="s">
         <v>377</v>
       </c>
-      <c r="G34" s="33" t="s">
+      <c r="G34" s="31" t="s">
         <v>378</v>
       </c>
-      <c r="H34" s="33" t="s">
+      <c r="H34" s="31" t="s">
         <v>745</v>
       </c>
-      <c r="I34" s="31" t="s">
+      <c r="I34" s="29" t="s">
         <v>756</v>
       </c>
       <c r="J34" s="18" t="s">
@@ -11627,36 +11603,36 @@
         <v>710</v>
       </c>
       <c r="O34" s="23" t="s">
-        <v>793</v>
+        <v>785</v>
       </c>
       <c r="P34" s="16"/>
       <c r="Q34" s="24" t="s">
         <v>688</v>
       </c>
     </row>
-    <row r="35" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="35" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B35" s="27">
         <v>31</v>
       </c>
-      <c r="C35" s="17" t="s">
-        <v>789</v>
+      <c r="C35" s="17">
+        <v>96050460</v>
       </c>
       <c r="D35" s="17" t="s">
         <v>382</v>
       </c>
-      <c r="E35" s="32" t="s">
+      <c r="E35" s="30" t="s">
         <v>17</v>
       </c>
       <c r="F35" s="18" t="s">
         <v>383</v>
       </c>
-      <c r="G35" s="33" t="s">
+      <c r="G35" s="31" t="s">
         <v>384</v>
       </c>
-      <c r="H35" s="33" t="s">
+      <c r="H35" s="31" t="s">
         <v>648</v>
       </c>
-      <c r="I35" s="31" t="s">
+      <c r="I35" s="29" t="s">
         <v>757</v>
       </c>
       <c r="J35" s="18" t="s">
@@ -11675,36 +11651,36 @@
         <v>711</v>
       </c>
       <c r="O35" s="23" t="s">
-        <v>792</v>
+        <v>784</v>
       </c>
       <c r="P35" s="16"/>
       <c r="Q35" s="24" t="s">
         <v>690</v>
       </c>
     </row>
-    <row r="36" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="36" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B36" s="27">
         <v>32</v>
       </c>
-      <c r="C36" s="17" t="s">
-        <v>790</v>
+      <c r="C36" s="17">
+        <v>96050464</v>
       </c>
       <c r="D36" s="17" t="s">
         <v>394</v>
       </c>
-      <c r="E36" s="32" t="s">
+      <c r="E36" s="30" t="s">
         <v>17</v>
       </c>
       <c r="F36" s="18" t="s">
         <v>395</v>
       </c>
-      <c r="G36" s="33" t="s">
+      <c r="G36" s="31" t="s">
         <v>396</v>
       </c>
-      <c r="H36" s="33" t="s">
+      <c r="H36" s="31" t="s">
         <v>747</v>
       </c>
-      <c r="I36" s="31" t="s">
+      <c r="I36" s="29" t="s">
         <v>758</v>
       </c>
       <c r="J36" s="18" t="s">
@@ -11723,7 +11699,7 @@
         <v>712</v>
       </c>
       <c r="O36" s="23" t="s">
-        <v>792</v>
+        <v>784</v>
       </c>
       <c r="P36" s="16"/>
       <c r="Q36" s="24" t="s">

--- a/format-laporan/hari-minggu-2026/Usulan Buka Rek PB Kab Maybrat 206 PB YOSUA KARETH.xlsx
+++ b/format-laporan/hari-minggu-2026/Usulan Buka Rek PB Kab Maybrat 206 PB YOSUA KARETH.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\BSPS-2026\format-laporan\hari-minggu-2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{830BBB74-F3C0-4350-AF68-097BAF23161A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0DCB911D-2A75-4876-8855-67E2AB39C762}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="897" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
